--- a/doc/游戏地图配置.xlsx
+++ b/doc/游戏地图配置.xlsx
@@ -466,7 +466,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -527,8 +527,10 @@
       <c r="F2" s="1">
         <v>0.1</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>14</v>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>60015, 6002, 6003</t>
+        </is>
       </c>
       <c r="H2" s="1" t="s">
         <v>15</v>
@@ -559,8 +561,10 @@
       <c r="F3" s="1">
         <v>0.1</v>
       </c>
-      <c r="G3" s="1">
-        <v>6001.0</v>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>6001, 60015</t>
+        </is>
       </c>
       <c r="H3" s="1" t="s">
         <v>15</v>
@@ -860,7 +864,59 @@
         <v>67</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>第一卷</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>60015</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>青石村野外</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>凡人俗世</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>低危探索</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6001, 6002</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1 天</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>刷怪池: 鸡, 稻草人</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>第一卷前期挂机打野区，可少量获取修为。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <drawing ns1:id="rId1"/>
 </worksheet>
 </file>